--- a/მომსახურების ანაზღაურება დელ.xlsx
+++ b/მომსახურების ანაზღაურება დელ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\deliverer\დეკლარაცია\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurts\OneDrive\სამუშაო დაფა\excelpdf\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DAE967D-F4C1-499D-B429-433F162213BD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9827B85C-047A-492B-BDBF-DBED0EC9D251}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="გადასატანი" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="თანხები" sheetId="2" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="108">
   <si>
     <t>8</t>
   </si>
@@ -337,6 +337,21 @@
   </si>
   <si>
     <t>კაცობაშვილი</t>
+  </si>
+  <si>
+    <t>ელიშაკოვი</t>
+  </si>
+  <si>
+    <t>ლუკას</t>
+  </si>
+  <si>
+    <t>კუპატაძე</t>
+  </si>
+  <si>
+    <t>01017046235</t>
+  </si>
+  <si>
+    <t>01027090847</t>
   </si>
 </sst>
 </file>
@@ -346,7 +361,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -384,6 +399,13 @@
       <color rgb="FF222222"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -434,7 +456,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -467,6 +489,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -749,13 +772,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G1048575"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="33.6640625" customWidth="1"/>
-    <col min="2" max="2" width="26.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.21875" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" customWidth="1"/>
+    <col min="1" max="1" width="33.6328125" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.1796875" customWidth="1"/>
+    <col min="6" max="6" width="14.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -783,26 +806,26 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="B2" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A2,ინფო!A:A,0))</f>
-        <v>საბა</v>
+        <v>დავითი</v>
       </c>
       <c r="C2" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A2,ინფო!A:A,0))</f>
-        <v>ცაგარეიშვილი</v>
+        <v>საყვარელიძე</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E2">
         <f>INDEX(თანხები!D:D,MATCH(A2,თანხები!A:A,0))</f>
-        <v>5144.63</v>
+        <v>6850.67</v>
       </c>
       <c r="F2" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A2,ინფო!A:A,0))</f>
-        <v>თბილისი</v>
+        <v>თბილისი გუდამაყრის ქ. N 2 ბ. 102</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>1</v>
@@ -810,26 +833,26 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="B3" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A3,ინფო!A:A,0))</f>
-        <v>ოთარ</v>
+        <v>საბა</v>
       </c>
       <c r="C3" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A3,ინფო!A:A,0))</f>
-        <v>კუპრეიშვილი</v>
+        <v>ცაგარეიშვილი</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E3">
         <f>INDEX(თანხები!D:D,MATCH(A3,თანხები!A:A,0))</f>
-        <v>4606</v>
+        <v>6123.55</v>
       </c>
       <c r="F3" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A3,ინფო!A:A,0))</f>
-        <v>საქართველო, ქალაქი ფოთი, უშანგი ჩხეიძის ქუჩა, N 3, ბინა 11</v>
+        <v>თბილისი</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>1</v>
@@ -837,22 +860,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>62003016407</v>
+        <v>47001040600</v>
       </c>
       <c r="B4" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A4,ინფო!A:A,0))</f>
-        <v>დავით</v>
+        <v>რობერტ</v>
       </c>
       <c r="C4" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A4,ინფო!A:A,0))</f>
-        <v>სვირავა</v>
+        <v>ელოიძე</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E4">
         <f>INDEX(თანხები!D:D,MATCH(A4,თანხები!A:A,0))</f>
-        <v>4514.6499999999996</v>
+        <v>5267.37</v>
       </c>
       <c r="F4" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A4,ინფო!A:A,0))</f>
@@ -863,27 +886,27 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5">
-        <v>47001040600</v>
+      <c r="A5" t="s">
+        <v>54</v>
       </c>
       <c r="B5" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A5,ინფო!A:A,0))</f>
-        <v>რობერტ</v>
+        <v>ნინო</v>
       </c>
       <c r="C5" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A5,ინფო!A:A,0))</f>
-        <v>ელოიძე</v>
+        <v>კვარაცხელია</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E5">
         <f>INDEX(თანხები!D:D,MATCH(A5,თანხები!A:A,0))</f>
-        <v>3630.53</v>
+        <v>4306.4799999999996</v>
       </c>
       <c r="F5" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A5,ინფო!A:A,0))</f>
-        <v>თბილისი</v>
+        <v>საქართველო, ქალაქი თბილისი, ფიროსმანის ქუჩა, N 3</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>1</v>
@@ -891,7 +914,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="B6" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A6,ინფო!A:A,0))</f>
@@ -899,18 +922,18 @@
       </c>
       <c r="C6" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A6,ინფო!A:A,0))</f>
-        <v>მეტრეველი</v>
+        <v>მელაძე</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E6">
         <f>INDEX(თანხები!D:D,MATCH(A6,თანხები!A:A,0))</f>
-        <v>3223.4</v>
+        <v>4267.5200000000004</v>
       </c>
       <c r="F6" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A6,ინფო!A:A,0))</f>
-        <v>თბილისი</v>
+        <v>საქართველო, ქალაქი თბილისი, ნიკოლოზ ანთელავას ქუჩა, N 4(ყოფ. პ. იბერის ქ.)</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>1</v>
@@ -918,7 +941,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="B7" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A7,ინფო!A:A,0))</f>
@@ -926,18 +949,18 @@
       </c>
       <c r="C7" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A7,ინფო!A:A,0))</f>
-        <v>მელაძე</v>
+        <v>მეტრეველი</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E7">
         <f>INDEX(თანხები!D:D,MATCH(A7,თანხები!A:A,0))</f>
-        <v>2901.5</v>
+        <v>4185.6099999999997</v>
       </c>
       <c r="F7" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A7,ინფო!A:A,0))</f>
-        <v>საქართველო, ქალაქი თბილისი, ნიკოლოზ ანთელავას ქუჩა, N 4(ყოფ. პ. იბერის ქ.)</v>
+        <v>თბილისი</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>1</v>
@@ -945,26 +968,26 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="B8" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A8,ინფო!A:A,0))</f>
-        <v>ნინო</v>
+        <v>ბადრი</v>
       </c>
       <c r="C8" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A8,ინფო!A:A,0))</f>
-        <v>კვარაცხელია</v>
+        <v>სირაძე</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E8">
         <f>INDEX(თანხები!D:D,MATCH(A8,თანხები!A:A,0))</f>
-        <v>2773.88</v>
+        <v>3712.89</v>
       </c>
       <c r="F8" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A8,ინფო!A:A,0))</f>
-        <v>საქართველო, ქალაქი თბილისი, ფიროსმანის ქუჩა, N 3</v>
+        <v>თბილისი გარდაბნის გზატ. N 42</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>1</v>
@@ -972,26 +995,26 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B9" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A9,ინფო!A:A,0))</f>
-        <v>მიხეილ</v>
+        <v>ოთარ</v>
       </c>
       <c r="C9" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A9,ინფო!A:A,0))</f>
-        <v>ლომჯარია</v>
+        <v>კუპრეიშვილი</v>
       </c>
       <c r="D9" s="8">
         <v>8</v>
       </c>
       <c r="E9">
         <f>INDEX(თანხები!D:D,MATCH(A9,თანხები!A:A,0))</f>
-        <v>1554.33</v>
+        <v>3305.06</v>
       </c>
       <c r="F9" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A9,ინფო!A:A,0))</f>
-        <v>საქართველო, ქალაქი თბილისი, შალვა ნუცუბიძის ფერდობი, IV მიკრო/რაიონი, კორპუსი 12, ბინა 3</v>
+        <v>საქართველო, ქალაქი ფოთი, უშანგი ჩხეიძის ქუჩა, N 3, ბინა 11</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>1</v>
@@ -999,53 +1022,53 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="B10" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A10,ინფო!A:A,0))</f>
-        <v>დავითი</v>
+        <v>მიხეილ</v>
       </c>
       <c r="C10" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A10,ინფო!A:A,0))</f>
-        <v>საყვარელიძე</v>
+        <v>ლომჯარია</v>
       </c>
       <c r="D10" s="8">
         <v>8</v>
       </c>
       <c r="E10">
         <f>INDEX(თანხები!D:D,MATCH(A10,თანხები!A:A,0))</f>
-        <v>1004.5</v>
+        <v>2962.01</v>
       </c>
       <c r="F10" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A10,ინფო!A:A,0))</f>
-        <v>თბილისი გუდამაყრის ქ. N 2 ბ. 102</v>
+        <v>საქართველო, ქალაქი თბილისი, შალვა ნუცუბიძის ფერდობი, IV მიკრო/რაიონი, კორპუსი 12, ბინა 3</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>64</v>
+      <c r="A11">
+        <v>62003016407</v>
       </c>
       <c r="B11" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A11,ინფო!A:A,0))</f>
-        <v>ბადრი</v>
+        <v>დავით</v>
       </c>
       <c r="C11" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A11,ინფო!A:A,0))</f>
-        <v>სირაძე</v>
+        <v>სვირავა</v>
       </c>
       <c r="D11" s="8">
         <v>8</v>
       </c>
       <c r="E11">
         <f>INDEX(თანხები!D:D,MATCH(A11,თანხები!A:A,0))</f>
-        <v>831.85</v>
+        <v>992.53</v>
       </c>
       <c r="F11" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A11,ინფო!A:A,0))</f>
-        <v>თბილისი გარდაბნის გზატ. N 42</v>
+        <v>თბილისი</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>1</v>
@@ -1053,22 +1076,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B12" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A12,ინფო!A:A,0))</f>
-        <v>ბენი</v>
+        <v>ლუკას</v>
       </c>
       <c r="C12" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A12,ინფო!A:A,0))</f>
-        <v>კაცობაშვილი</v>
+        <v>ელიშაკოვი</v>
       </c>
       <c r="D12" s="8">
         <v>8</v>
       </c>
       <c r="E12">
         <f>INDEX(თანხები!D:D,MATCH(A12,თანხები!A:A,0))</f>
-        <v>7.12</v>
+        <v>970.3</v>
       </c>
       <c r="F12" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A12,ინფო!A:A,0))</f>
@@ -1079,24 +1102,27 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="B13" s="8" t="e">
+      <c r="A13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(A13,ინფო!A:A,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C13" s="8" t="e">
+        <v>საბა</v>
+      </c>
+      <c r="C13" s="8" t="str">
         <f>INDEX(ინფო!C:C,MATCH(A13,ინფო!A:A,0))</f>
-        <v>#N/A</v>
+        <v>კუპატაძე</v>
       </c>
       <c r="D13" s="8">
         <v>8</v>
       </c>
-      <c r="E13" t="e">
+      <c r="E13">
         <f>INDEX(თანხები!D:D,MATCH(A13,თანხები!A:A,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F13" s="5" t="e">
+        <v>560.46</v>
+      </c>
+      <c r="F13" s="5" t="str">
         <f>INDEX(ინფო!D:D,MATCH(A13,ინფო!A:A,0))</f>
-        <v>#N/A</v>
+        <v>თბილისი</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>1</v>
@@ -1208,13 +1234,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{604AE93E-E511-4BD8-A9E1-AE041AC99209}">
-  <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" customWidth="1"/>
-    <col min="4" max="4" width="87.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" customWidth="1"/>
+    <col min="4" max="4" width="87.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1606,6 +1632,34 @@
         <v>102</v>
       </c>
       <c r="D28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" t="s">
+        <v>103</v>
+      </c>
+      <c r="D29" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" t="s">
+        <v>105</v>
+      </c>
+      <c r="D30" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1618,12 +1672,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7E4943-2DCB-430A-830C-82E1F3476269}">
   <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="21.21875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" customWidth="1"/>
-    <col min="3" max="3" width="18.109375" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1796875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="19.54296875" customWidth="1"/>
+    <col min="3" max="3" width="18.08984375" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" style="17" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1644,195 +1698,199 @@
     <row r="2" spans="1:5">
       <c r="A2" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C2,ინფო!C:C,0))</f>
-        <v>01001083359</v>
+        <v>38001048993</v>
       </c>
       <c r="B2" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C2,ინფო!C:C,0))</f>
-        <v>საბა</v>
+        <v>დავითი</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="D2" s="19">
-        <v>5144.63</v>
+        <v>6850.67</v>
       </c>
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C3,ინფო!C:C,0))</f>
-        <v>42401042214</v>
+        <v>01001083359</v>
       </c>
       <c r="B3" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C3,ინფო!C:C,0))</f>
-        <v>ოთარ</v>
+        <v>საბა</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="D3" s="19">
-        <v>4606</v>
+        <v>6123.55</v>
       </c>
       <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
         <f>INDEX(ინფო!A:A,MATCH(C4,ინფო!C:C,0))</f>
-        <v>62003016407</v>
+        <v>47001040600</v>
       </c>
       <c r="B4" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C4,ინფო!C:C,0))</f>
-        <v>დავით</v>
+        <v>რობერტ</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D4" s="19">
-        <v>4514.6499999999996</v>
+        <v>5267.37</v>
       </c>
       <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5">
+      <c r="A5" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C5,ინფო!C:C,0))</f>
-        <v>47001040600</v>
+        <v>01030053301</v>
       </c>
       <c r="B5" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C5,ინფო!C:C,0))</f>
-        <v>რობერტ</v>
+        <v>ნინო</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="D5" s="19">
-        <v>3630.53</v>
+        <v>4306.4799999999996</v>
       </c>
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C6,ინფო!C:C,0))</f>
-        <v>01401103956</v>
+        <v>01030053229</v>
       </c>
       <c r="B6" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C6,ინფო!C:C,0))</f>
         <v>გიორგი</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="D6" s="19">
-        <v>3223.4</v>
+        <v>4267.5200000000004</v>
       </c>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C7,ინფო!C:C,0))</f>
-        <v>01030053229</v>
+        <v>01401103956</v>
       </c>
       <c r="B7" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C7,ინფო!C:C,0))</f>
         <v>გიორგი</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="D7" s="19">
-        <v>2901.5</v>
+        <v>4185.6099999999997</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C8,ინფო!C:C,0))</f>
-        <v>01030053301</v>
+        <v>22001020425</v>
       </c>
       <c r="B8" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C8,ინფო!C:C,0))</f>
-        <v>ნინო</v>
+        <v>ბადრი</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="D8" s="19">
-        <v>2773.88</v>
+        <v>3712.89</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C9,ინფო!C:C,0))</f>
-        <v>01010000461</v>
+        <v>42401042214</v>
       </c>
       <c r="B9" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C9,ინფო!C:C,0))</f>
-        <v>მიხეილ</v>
+        <v>ოთარ</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D9" s="19">
-        <v>1554.33</v>
+        <v>3305.06</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C10,ინფო!C:C,0))</f>
-        <v>38001048993</v>
+        <v>01010000461</v>
       </c>
       <c r="B10" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C10,ინფო!C:C,0))</f>
-        <v>დავითი</v>
+        <v>მიხეილ</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D10" s="19">
-        <v>1004.5</v>
+        <v>2962.01</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" t="str">
+      <c r="A11">
         <f>INDEX(ინფო!A:A,MATCH(C11,ინფო!C:C,0))</f>
-        <v>22001020425</v>
+        <v>62003016407</v>
       </c>
       <c r="B11" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C11,ინფო!C:C,0))</f>
-        <v>ბადრი</v>
+        <v>დავით</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="D11" s="19">
-        <v>831.85</v>
+        <v>992.53</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C12,ინფო!C:C,0))</f>
-        <v>01017036626</v>
+        <v>01017046235</v>
       </c>
       <c r="B12" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C12,ინფო!C:C,0))</f>
-        <v>ბენი</v>
+        <v>ლუკას</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" s="19">
-        <v>7.12</v>
+        <v>970.3</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" t="e">
+      <c r="A13" t="str">
         <f>INDEX(ინფო!A:A,MATCH(C13,ინფო!C:C,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="B13" t="e">
+        <v>01027090847</v>
+      </c>
+      <c r="B13" t="str">
         <f>INDEX(ინფო!B:B,MATCH(C13,ინფო!C:C,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
+        <v>საბა</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" s="19">
+        <v>560.46</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="e">
@@ -1916,12 +1974,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21D28A8-2A04-4213-9FF0-5FC7E21D8E88}">
   <dimension ref="A3:K19"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" style="13" customWidth="1"/>
-    <col min="3" max="3" width="25.6640625" style="18" customWidth="1"/>
-    <col min="4" max="4" width="25.6640625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.81640625" style="13" customWidth="1"/>
+    <col min="3" max="3" width="25.6328125" style="18" customWidth="1"/>
+    <col min="4" max="4" width="25.6328125" customWidth="1"/>
+    <col min="6" max="6" width="14.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:11">
@@ -1933,107 +1991,112 @@
     <row r="5" spans="1:11">
       <c r="A5" s="14"/>
       <c r="C5" s="19" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="D5" s="19">
-        <v>5144.63</v>
+        <v>6850.67</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="15"/>
       <c r="C6" s="19" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="D6" s="19">
-        <v>4606</v>
+        <v>6123.55</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="C7" s="19" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D7" s="19">
-        <v>4514.6499999999996</v>
+        <v>5267.37</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="15"/>
       <c r="C8" s="19" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="D8" s="19">
-        <v>3630.53</v>
+        <v>4306.4799999999996</v>
       </c>
       <c r="K8" s="17"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="15"/>
       <c r="C9" s="19" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="D9" s="19">
-        <v>3223.4</v>
+        <v>4267.5200000000004</v>
       </c>
       <c r="K9" s="17"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="15"/>
       <c r="C10" s="19" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="D10" s="19">
-        <v>2901.5</v>
+        <v>4185.6099999999997</v>
       </c>
       <c r="K10" s="17"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="15"/>
       <c r="C11" s="19" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="D11" s="19">
-        <v>2773.88</v>
+        <v>3712.89</v>
       </c>
       <c r="K11" s="17"/>
     </row>
     <row r="12" spans="1:11">
       <c r="C12" s="19" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D12" s="19">
-        <v>1554.33</v>
+        <v>3305.06</v>
       </c>
       <c r="K12" s="17"/>
     </row>
     <row r="13" spans="1:11">
       <c r="C13" s="19" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D13" s="19">
-        <v>1004.5</v>
+        <v>2962.01</v>
       </c>
       <c r="K13" s="17"/>
     </row>
     <row r="14" spans="1:11">
       <c r="C14" s="19" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="D14" s="19">
-        <v>831.85</v>
+        <v>992.53</v>
       </c>
       <c r="K14" s="17"/>
     </row>
     <row r="15" spans="1:11">
       <c r="C15" s="19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D15" s="19">
-        <v>7.12</v>
+        <v>970.3</v>
       </c>
       <c r="K15" s="17"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="D16" s="18"/>
+      <c r="C16" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="19">
+        <v>560.46</v>
+      </c>
       <c r="K16" s="17"/>
     </row>
     <row r="17" spans="11:11">

--- a/მომსახურების ანაზღაურება დელ.xlsx
+++ b/მომსახურების ანაზღაურება დელ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurts\OneDrive\სამუშაო დაფა\excelpdf\bank-summary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9827B85C-047A-492B-BDBF-DBED0EC9D251}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4068CC87-E251-43C9-8239-505C8A9CEBBC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="გადასატანი" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="თანხები" sheetId="2" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -772,13 +772,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G1048575"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="33.6328125" customWidth="1"/>
-    <col min="2" max="2" width="26.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.1796875" customWidth="1"/>
-    <col min="6" max="6" width="14.36328125" customWidth="1"/>
+    <col min="1" max="1" width="33.6640625" customWidth="1"/>
+    <col min="2" max="2" width="26.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.21875" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1235,12 +1235,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{604AE93E-E511-4BD8-A9E1-AE041AC99209}">
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" customWidth="1"/>
-    <col min="3" max="3" width="16.08984375" customWidth="1"/>
-    <col min="4" max="4" width="87.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" customWidth="1"/>
+    <col min="4" max="4" width="87.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1672,12 +1672,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7E4943-2DCB-430A-830C-82E1F3476269}">
   <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="21.1796875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" customWidth="1"/>
-    <col min="3" max="3" width="18.08984375" customWidth="1"/>
-    <col min="4" max="4" width="9.08984375" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.21875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" customWidth="1"/>
+    <col min="3" max="3" width="18.109375" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="17" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1974,12 +1974,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E21D28A8-2A04-4213-9FF0-5FC7E21D8E88}">
   <dimension ref="A3:K19"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" style="13" customWidth="1"/>
-    <col min="3" max="3" width="25.6328125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="25.6328125" customWidth="1"/>
-    <col min="6" max="6" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.77734375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" style="18" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:11">
